--- a/04_DESIGN_TABLES/DesignTable_6405_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6405_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG41"/>
+  <dimension ref="A1:AG45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,32 +697,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6405-03-04-O</t>
+          <t>6405-02-02-O</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.43301</v>
+        <v>0.32447</v>
       </c>
       <c r="D3" t="n">
-        <v>0.75</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1875</v>
+        <v>0.15625</v>
       </c>
       <c r="F3" t="n">
         <v>0.234</v>
       </c>
       <c r="G3" t="n">
-        <v>0.156</v>
+        <v>0.125</v>
       </c>
       <c r="H3" t="n">
         <v>0.063</v>
       </c>
       <c r="I3" t="n">
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="J3" t="n">
         <v>0.04167</v>
@@ -740,43 +740,43 @@
         <v>0.04167</v>
       </c>
       <c r="O3" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="P3" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="R3" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="T3" t="n">
-        <v>0.215</v>
+        <v>0.165</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2594</v>
+        <v>0.1946</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="W3" t="n">
-        <v>0.13</v>
+        <v>0.062</v>
       </c>
       <c r="X3" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>6405-03-04-O</t>
+          <t>6405-02-02-O</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/8-24 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 5/16-24 (male ORB) x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>3/8-24 (male ORB)</t>
+          <t>5/16-24 (male ORB)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -801,98 +801,103 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L31@DRIVE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-02-O col "L LGTH" = "0.950" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 640.5, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 3/5 rows with an Air-Way/OMi value agree with this catalog column to rounding (2 differ, e.g. 6405-03-04-O 1.1 vs 1.2); HEXB@HEX: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-02-O col "C4 HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 640.5, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-02-O col "B DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 640.5, page verified) [Brennan = yes 2026-10-18] - bore from the ORB end; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_A@DRIVE: end library gen_straight2 ORB[2] (src: 6408-02-O-SOLID row; MS51527G / MS51528D J2, Parker ORD-5700 Table 4-4) [Q-TRANSFER-ENDLIB yes] thread major; FPT_P1@DRIVE: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) port depth (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: thread text from the part-number dash, format of the built 6405 rows; $PRP@EndB_Thread: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) thread text | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom; male ORB -02 end (5/16-24): thread length 0.234, groove root dia 0.250, groove width 0.063 taken from the 6408-02-O-SOLID review row (MS51527G / MS51528D J2 thread length; Parker ORD-5700 Table 4-4 F / G, O-ring 3-902) - the same fixed ORB stud end on every series, as -03..-32 (ASSUMPTION); thread length and groove root dia = the Brennan 6801-04-02-NWO-FG STEP (adjustable stud); groove width single source (ORD-5700); no Brennan STEP with a fixed -02 ORB end yet</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L31 / hex / D3 from the Brennan TFA catalog p15 alone; ORB -02 end from the 6408-02-O-SOLID row library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6405-03-04-O</t>
+          <t>6405-02-02-O</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6405-04-02-O</t>
+          <t>6405-02-04-O</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.97</v>
+        <v>1.24</v>
       </c>
       <c r="C4" t="n">
-        <v>0.32332</v>
+        <v>0.43301</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.265</v>
+        <v>0.234</v>
       </c>
       <c r="G4" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="K4" t="n">
-        <v>0.265</v>
+        <v>0.234</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="O4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="P4" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="R4" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="S4" t="n">
-        <v>0.037</v>
+        <v>0.0556</v>
       </c>
       <c r="T4" t="n">
-        <v>0.165</v>
+        <v>0.215</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1946</v>
+        <v>0.2594</v>
       </c>
       <c r="V4" t="n">
-        <v>0.97</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="X4" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6405-04-02-O</t>
+          <t>6405-02-04-O</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/16-20 (male ORB) x 1/8-27 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 5/16-24 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -902,12 +907,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>7/16-20 (male ORB)</t>
+          <t>5/16-24 (male ORB)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -917,23 +922,28 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L31@DRIVE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-04-O col "L LGTH" = "1.240" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 650.6, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 3/5 rows with an Air-Way/OMi value agree with this catalog column to rounding (2 differ, e.g. 6405-03-04-O 1.1 vs 1.2); HEXB@HEX: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-04-O col "C4 HEX" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 650.6, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; D3@BORE: Brennan TFA catalog p15 table TFA-p015-t04 "6405-O MORB-FP STRAIGHT" row 6405-02-04-O col "B DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 650.6, page verified) [Brennan = yes 2026-10-18] - bore from the ORB end; mapping: TFA p15 6405-O drawing: L = overall, C4 HEX = body hex, B DRILL = drill from the ORB end = D3 (impact/F2b.json, certain); same-table check on today's base: 5/5 rows with an Air-Way/OMi value agree with this catalog column to rounding; THDMAJ_A@DRIVE: end library gen_straight2 ORB[2] (src: 6408-02-O-SOLID row; MS51527G / MS51528D J2, Parker ORD-5700 Table 4-4) [Q-TRANSFER-ENDLIB yes] thread major; FPT_P1@DRIVE: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) port depth (end detail) [Q-TRANSFER-ENDLIB yes]; TAPDRILL@BORE_A: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; $PRP@EndA_Thread: thread text from the part-number dash, format of the built 6405 rows; $PRP@EndB_Thread: end library gen_straight2 FPT[4] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.43, FPT_P1 0.67 = MS51503 P1 max) thread text | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom; male ORB -02 end (5/16-24): thread length 0.234, groove root dia 0.250, groove width 0.063 taken from the 6408-02-O-SOLID review row (MS51527G / MS51528D J2 thread length; Parker ORD-5700 Table 4-4 F / G, O-ring 3-902) - the same fixed ORB stud end on every series, as -03..-32 (ASSUMPTION); thread length and groove root dia = the Brennan 6801-04-02-NWO-FG STEP (adjustable stud); groove width single source (ORD-5700); no Brennan STEP with a fixed -02 ORB end yet</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L31 / hex / D3 from the Brennan TFA catalog p15 alone; ORB -02 end from the 6408-02-O-SOLID row library; tap drill = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6405-04-02-O</t>
+          <t>6405-02-04-O</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6405-04-04-O</t>
+          <t>6405-03-04-O</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="C5" t="n">
         <v>0.43301</v>
@@ -942,34 +952,34 @@
         <v>0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>0.21875</v>
+        <v>0.1875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.265</v>
+        <v>0.234</v>
       </c>
       <c r="G5" t="n">
-        <v>0.182</v>
+        <v>0.156</v>
       </c>
       <c r="H5" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="K5" t="n">
-        <v>0.265</v>
+        <v>0.234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="O5" t="n">
         <v>0.43</v>
@@ -993,22 +1003,22 @@
         <v>0.2594</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>6405-04-04-O</t>
+          <t>6405-03-04-O</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/16-20 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/8-24 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1018,7 +1028,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>7/16-20 (male ORB)</t>
+          <t>3/8-24 (male ORB)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1038,24 +1048,24 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6405-04-04-O</t>
+          <t>6405-03-04-O</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6405-04-06-O</t>
+          <t>6405-04-02-O</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.35</v>
+        <v>0.97</v>
       </c>
       <c r="C6" t="n">
-        <v>0.50807</v>
+        <v>0.32332</v>
       </c>
       <c r="D6" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
         <v>0.21875</v>
@@ -1088,43 +1098,43 @@
         <v>0.05</v>
       </c>
       <c r="O6" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="P6" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="R6" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="T6" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3294</v>
+        <v>0.1946</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0.97</v>
       </c>
       <c r="W6" t="n">
         <v>0.17</v>
       </c>
       <c r="X6" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6405-04-06-O</t>
+          <t>6405-04-02-O</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/16-20 (male ORB) x 3/8-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/16-20 (male ORB) x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1139,7 +1149,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1149,44 +1159,44 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1766 Overall Length = 1.350 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6405-04-06-O</t>
+          <t>6405-04-02-O</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6405-05-02-O</t>
+          <t>6405-04-04-O</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.36373</v>
+        <v>0.43301</v>
       </c>
       <c r="D7" t="n">
-        <v>0.63</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="F7" t="n">
         <v>0.265</v>
       </c>
       <c r="G7" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="H7" t="n">
         <v>0.075</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="J7" t="n">
         <v>0.05</v>
@@ -1204,43 +1214,43 @@
         <v>0.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="P7" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="R7" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="S7" t="n">
-        <v>0.037</v>
+        <v>0.0556</v>
       </c>
       <c r="T7" t="n">
-        <v>0.165</v>
+        <v>0.215</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1946</v>
+        <v>0.2594</v>
       </c>
       <c r="V7" t="n">
-        <v>0.99</v>
+        <v>1.16</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="X7" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>6405-05-02-O</t>
+          <t>6405-04-04-O</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1/2-20 (male ORB) x 1/8-27 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/16-20 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1250,12 +1260,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>1/2-20 (male ORB)</t>
+          <t>7/16-20 (male ORB)</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1265,44 +1275,44 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1767 Overall Length = 0.990 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6405-05-02-O</t>
+          <t>6405-04-04-O</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6405-05-04-O</t>
+          <t>6405-04-06-O</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="C8" t="n">
-        <v>0.43301</v>
+        <v>0.50807</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="F8" t="n">
         <v>0.265</v>
       </c>
       <c r="G8" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="H8" t="n">
         <v>0.075</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="J8" t="n">
         <v>0.05</v>
@@ -1320,43 +1330,43 @@
         <v>0.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="P8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="R8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="S8" t="n">
         <v>0.0556</v>
       </c>
       <c r="T8" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2594</v>
+        <v>0.3294</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>6405-05-04-O</t>
+          <t>6405-04-06-O</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1/2-20 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/16-20 (male ORB) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1366,12 +1376,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>1/2-20 (male ORB)</t>
+          <t>7/16-20 (male ORB)</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1381,59 +1391,59 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1768 Overall Length = 1.200 (table had 1.15) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1766 Overall Length = 1.350 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6405-05-04-O</t>
+          <t>6405-04-06-O</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6405-06-02-O</t>
+          <t>6405-05-02-O</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="C9" t="n">
-        <v>0.39837</v>
+        <v>0.36373</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="E9" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="H9" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O9" t="n">
         <v>0.33</v>
@@ -1457,22 +1467,22 @@
         <v>0.1946</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="W9" t="n">
-        <v>0.297</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>6405-06-02-O</t>
+          <t>6405-05-02-O</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 1/8-27 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1/2-20 (male ORB) x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1482,7 +1492,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>9/16-18 (male ORB)</t>
+          <t>1/2-20 (male ORB)</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1497,28 +1507,23 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1769 Overall Length = 1.020 (table had 0.73); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1769 Side 1 ID = 0.297 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.297 - column bleed suspected, as-printed</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1767 Overall Length = 0.990 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6405-06-02-O</t>
+          <t>6405-05-02-O</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6405-06-04-O</t>
+          <t>6405-05-04-O</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="C10" t="n">
         <v>0.43301</v>
@@ -1527,34 +1532,34 @@
         <v>0.75</v>
       </c>
       <c r="E10" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="H10" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.312</v>
+        <v>0.265</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O10" t="n">
         <v>0.43</v>
@@ -1578,22 +1583,22 @@
         <v>0.2594</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6405-06-04-O</t>
+          <t>6405-05-04-O</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1/2-20 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1603,7 +1608,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>9/16-18 (male ORB)</t>
+          <t>1/2-20 (male ORB)</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1618,34 +1623,29 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1770 Overall Length = 1.090 (table had 1.18); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1770 Hex Flat = 0.750 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.420 to the far tip, inside the other end's thread/groove region (0.395) - Air-Way L 1.09 looks suspect for this size (built as printed)</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1768 Overall Length = 1.200 (table had 1.15) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6405-06-04-O</t>
+          <t>6405-05-04-O</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6405-06-06-O</t>
+          <t>6405-06-02-O</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="C11" t="n">
-        <v>0.50807</v>
+        <v>0.39837</v>
       </c>
       <c r="D11" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.28125</v>
@@ -1678,43 +1678,43 @@
         <v>0.05556</v>
       </c>
       <c r="O11" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="R11" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="T11" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3294</v>
+        <v>0.1946</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="X11" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>6405-06-06-O</t>
+          <t>6405-06-02-O</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 3/8-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1739,29 +1739,34 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1771 Overall Length = 1.330 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1769 Overall Length = 1.020 (table had 0.73); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1769 Side 1 ID = 0.297 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.297 - column bleed suspected, as-printed</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6405-06-06-O</t>
+          <t>6405-06-02-O</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6405-06-08-O</t>
+          <t>6405-06-04-O</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="C12" t="n">
-        <v>0.65241</v>
+        <v>0.43301</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="n">
         <v>0.28125</v>
@@ -1794,43 +1799,43 @@
         <v>0.05556</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="S12" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="T12" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4071</v>
+        <v>0.2594</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
         <v>0.3</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>6405-06-08-O</t>
+          <t>6405-06-04-O</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 1/2-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1850,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1855,23 +1860,28 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1770 Overall Length = 1.090 (table had 1.18); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1770 Hex Flat = 0.750 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.420 to the far tip, inside the other end's thread/groove region (0.395) - Air-Way L 1.09 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6405-06-08-O</t>
+          <t>6405-06-04-O</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6405-08-02-O</t>
+          <t>6405-06-06-O</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="C13" t="n">
         <v>0.50807</v>
@@ -1880,73 +1890,73 @@
         <v>0.88</v>
       </c>
       <c r="E13" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F13" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="G13" t="n">
-        <v>0.33</v>
+        <v>0.2405</v>
       </c>
       <c r="H13" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="I13" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="K13" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O13" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="P13" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="S13" t="n">
-        <v>0.037</v>
+        <v>0.0556</v>
       </c>
       <c r="T13" t="n">
-        <v>0.165</v>
+        <v>0.285</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1946</v>
+        <v>0.3294</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0.34</v>
+        <v>0.65</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>6405-08-02-O</t>
+          <t>6405-06-06-O</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 1/8-27 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,12 +1966,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3/4-16 (male ORB)</t>
+          <t>9/16-18 (male ORB)</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1/8-27 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -1971,103 +1981,98 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1773 Side 1 ID = 0.315 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.46 leaves only 0.340 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 0.8 looks suspect for this size (built as printed)</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1771 Overall Length = 1.330 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>6405-08-02-O</t>
+          <t>6405-06-06-O</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6405-08-04-O</t>
+          <t>6405-06-08-O</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.50807</v>
+        <v>0.65241</v>
       </c>
       <c r="D14" t="n">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F14" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="G14" t="n">
-        <v>0.33</v>
+        <v>0.2405</v>
       </c>
       <c r="H14" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="I14" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="K14" t="n">
-        <v>0.344</v>
+        <v>0.312</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O14" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="P14" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.215</v>
+        <v>0.35</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2594</v>
+        <v>0.4071</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0.391</v>
+        <v>0.3</v>
       </c>
       <c r="X14" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>6405-08-04-O</t>
+          <t>6405-06-08-O</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 9/16-18 (male ORB) x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,43 +2082,43 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>3/4-16 (male ORB)</t>
+          <t>9/16-18 (male ORB)</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1774 Side 1 ID = 0.391 (table had 0.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.350 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 1.02 looks suspect for this size (built as printed)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.5~1.500; HEXB@HEX=1.13~1.125; D3@BORE=0.3~0.297</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6405-08-04-O</t>
+          <t>6405-06-08-O</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6405-08-06-O</t>
+          <t>6405-08-02-O</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.28</v>
+        <v>0.8</v>
       </c>
       <c r="C15" t="n">
         <v>0.50807</v>
@@ -2152,43 +2157,43 @@
         <v>0.0625</v>
       </c>
       <c r="O15" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="P15" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0556</v>
+        <v>0.037</v>
       </c>
       <c r="T15" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3294</v>
+        <v>0.1946</v>
       </c>
       <c r="V15" t="n">
-        <v>1.28</v>
+        <v>0.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0.39</v>
+        <v>0.315</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>6405-08-06-O</t>
+          <t>6405-08-02-O</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 3/8-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2208,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>1/8-27 NPTF (female)</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2213,29 +2218,34 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1775 Overall Length = 1.280 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1773 Side 1 ID = 0.315 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.46 leaves only 0.340 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 0.8 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6405-08-06-O</t>
+          <t>6405-08-02-O</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6405-08-12-O</t>
+          <t>6405-08-04-O</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="C16" t="n">
-        <v>0.79674</v>
+        <v>0.50807</v>
       </c>
       <c r="D16" t="n">
-        <v>1.38</v>
+        <v>0.88</v>
       </c>
       <c r="E16" t="n">
         <v>0.375</v>
@@ -2268,43 +2278,43 @@
         <v>0.0625</v>
       </c>
       <c r="O16" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="P16" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.91</v>
+        <v>0.43</v>
       </c>
       <c r="R16" t="n">
-        <v>0.91</v>
+        <v>0.67</v>
       </c>
       <c r="S16" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="T16" t="n">
-        <v>0.455</v>
+        <v>0.215</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5121</v>
+        <v>0.2594</v>
       </c>
       <c r="V16" t="n">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="X16" t="n">
-        <v>0.87</v>
+        <v>0.35</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>6405-08-12-O</t>
+          <t>6405-08-04-O</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 3/4-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,7 +2329,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -2329,98 +2339,103 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1777 Overall Length = 1.780 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1774 Side 1 ID = 0.391 (table had 0.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.350 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 1.02 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6405-08-12-O</t>
+          <t>6405-08-04-O</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6405-10-04-O</t>
+          <t>6405-08-06-O</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
       <c r="C17" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3865</v>
+        <v>0.33</v>
       </c>
       <c r="H17" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="I17" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="K17" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O17" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="P17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="R17" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="S17" t="n">
         <v>0.0556</v>
       </c>
       <c r="T17" t="n">
-        <v>0.215</v>
+        <v>0.285</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2594</v>
+        <v>0.3294</v>
       </c>
       <c r="V17" t="n">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="X17" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>6405-10-04-O</t>
+          <t>6405-08-06-O</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2430,12 +2445,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>7/8-14 (male ORB)</t>
+          <t>3/4-16 (male ORB)</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -2445,103 +2460,98 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.484 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.260 to the far tip, inside the other end's thread/groove region (0.498) - Air-Way L 0.93 looks suspect for this size (built as printed)</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1775 Overall Length = 1.280 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6405-10-04-O</t>
+          <t>6405-08-06-O</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6405-10-06-O</t>
+          <t>6405-08-12-O</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="C18" t="n">
-        <v>0.57735</v>
+        <v>0.79674</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F18" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3865</v>
+        <v>0.33</v>
       </c>
       <c r="H18" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="I18" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="J18" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="K18" t="n">
-        <v>0.391</v>
+        <v>0.344</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O18" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="P18" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="R18" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.285</v>
+        <v>0.455</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3294</v>
+        <v>0.5121</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="W18" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="X18" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>6405-10-06-O</t>
+          <t>6405-08-12-O</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 3/8-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 3/4-16 (male ORB) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2551,12 +2561,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>7/8-14 (male ORB)</t>
+          <t>3/4-16 (male ORB)</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2566,29 +2576,29 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1780 Overall Length = 1.400 (table had 1.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1777 Overall Length = 1.780 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6405-10-06-O</t>
+          <t>6405-08-12-O</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6405-10-08-O</t>
+          <t>6405-10-04-O</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.55</v>
+        <v>0.93</v>
       </c>
       <c r="C19" t="n">
-        <v>0.65241</v>
+        <v>0.57735</v>
       </c>
       <c r="D19" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0.4375</v>
@@ -2621,43 +2631,43 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="S19" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="T19" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4071</v>
+        <v>0.2594</v>
       </c>
       <c r="V19" t="n">
-        <v>1.55</v>
+        <v>0.93</v>
       </c>
       <c r="W19" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="X19" t="n">
-        <v>0.65</v>
+        <v>0.26</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>6405-10-08-O</t>
+          <t>6405-10-04-O</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 1/2-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2672,12 +2682,12 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -2685,26 +2695,31 @@
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.484 - column bleed suspected, as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=0.93~0.930; HEXB@HEX=1~1.000; D3@BORE=0.43~0.431 | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.260 to the far tip, inside the other end's thread/groove region (0.498) - Air-Way L 0.93 looks suspect for this size (built as printed)</t>
+        </is>
+      </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6405-10-08-O</t>
+          <t>6405-10-04-O</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6405-10-12-O</t>
+          <t>6405-10-06-O</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="C20" t="n">
-        <v>0.79674</v>
+        <v>0.57735</v>
       </c>
       <c r="D20" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0.4375</v>
@@ -2737,43 +2752,43 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="P20" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="R20" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="T20" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5121</v>
+        <v>0.3294</v>
       </c>
       <c r="V20" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
         <v>0.48</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>6405-10-12-O</t>
+          <t>6405-10-06-O</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 3/4-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2788,7 +2803,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -2798,98 +2813,98 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1782 Overall Length = 1.710 (table had 1.64) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1780 Overall Length = 1.400 (table had 1.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6405-10-12-O</t>
+          <t>6405-10-06-O</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6405-12-04-O</t>
+          <t>6405-10-08-O</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.65241</v>
       </c>
       <c r="D21" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="E21" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F21" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="H21" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="M21" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="N21" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="P21" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="R21" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.215</v>
+        <v>0.35</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2594</v>
+        <v>0.4071</v>
       </c>
       <c r="V21" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="X21" t="n">
-        <v>0.42</v>
+        <v>0.65</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>6405-12-04-O</t>
+          <t>6405-10-08-O</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,17 +2914,17 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>1 1/16-12 (male ORB)</t>
+          <t>7/8-14 (male ORB)</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -2919,98 +2934,98 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.43); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.420 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.09 looks suspect for this size (built as printed)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.55~1.550; HEXB@HEX=1.13~1.125; D3@BORE=0.48~0.484</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6405-12-04-O</t>
+          <t>6405-10-08-O</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6405-12-06-O</t>
+          <t>6405-10-12-O</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.79674</v>
       </c>
       <c r="D22" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="E22" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F22" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4725</v>
+        <v>0.3865</v>
       </c>
       <c r="H22" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="L22" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="M22" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="N22" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="P22" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="R22" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0556</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.285</v>
+        <v>0.455</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3294</v>
+        <v>0.5121</v>
       </c>
       <c r="V22" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="W22" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="X22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>6405-12-06-O</t>
+          <t>6405-10-12-O</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 3/8-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 7/8-14 (male ORB) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,12 +3035,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>1 1/16-12 (male ORB)</t>
+          <t>7/8-14 (male ORB)</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3035,28 +3050,23 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1784 Overall Length = 1.490 (table had 1.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.57); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1782 Overall Length = 1.710 (table had 1.64) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6405-12-06-O</t>
+          <t>6405-10-12-O</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6405-12-08-O</t>
+          <t>6405-12-04-O</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="C23" t="n">
         <v>0.7216900000000001</v>
@@ -3095,43 +3105,43 @@
         <v>0.08333</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="S23" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="T23" t="n">
-        <v>0.35</v>
+        <v>0.215</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4071</v>
+        <v>0.2594</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>0.61</v>
+        <v>0.43</v>
       </c>
       <c r="X23" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>6405-12-08-O</t>
+          <t>6405-12-04-O</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 1/2-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3156,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -3156,34 +3166,34 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1785 Overall Length = 1.410 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.510 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.41 looks suspect for this size (built as printed)</t>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.43); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.420 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.09 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6405-12-08-O</t>
+          <t>6405-12-04-O</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6405-12-12-O</t>
+          <t>6405-12-06-O</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="C24" t="n">
-        <v>0.79674</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0.53125</v>
@@ -3216,43 +3226,43 @@
         <v>0.08333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="P24" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="R24" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="S24" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="T24" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5121</v>
+        <v>0.3294</v>
       </c>
       <c r="V24" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="X24" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>6405-12-12-O</t>
+          <t>6405-12-06-O</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 3/4-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3267,7 +3277,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -3277,29 +3287,34 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1784 Overall Length = 1.490 (table had 1.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.57); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>6405-12-12-O</t>
+          <t>6405-12-06-O</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6405-12-16-O</t>
+          <t>6405-12-08-O</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.03</v>
+        <v>1.41</v>
       </c>
       <c r="C25" t="n">
-        <v>0.94108</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="E25" t="n">
         <v>0.53125</v>
@@ -3332,43 +3347,43 @@
         <v>0.08333</v>
       </c>
       <c r="O25" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="P25" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="S25" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="V25" t="n">
-        <v>2.03</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
         <v>0.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0.89</v>
+        <v>0.51</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>6405-12-16-O</t>
+          <t>6405-12-08-O</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3383,7 +3398,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -3393,23 +3408,28 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1787 Overall Length = 2.030 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1785 Overall Length = 1.410 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.510 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.41 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>6405-12-16-O</t>
+          <t>6405-12-08-O</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6405-14-12-O</t>
+          <t>6405-12-12-O</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="C26" t="n">
         <v>0.79674</v>
@@ -3418,19 +3438,19 @@
         <v>1.38</v>
       </c>
       <c r="E26" t="n">
-        <v>0.59375</v>
+        <v>0.53125</v>
       </c>
       <c r="F26" t="n">
         <v>0.469</v>
       </c>
       <c r="G26" t="n">
-        <v>0.535</v>
+        <v>0.4725</v>
       </c>
       <c r="H26" t="n">
         <v>0.125</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1875</v>
+        <v>1.0625</v>
       </c>
       <c r="J26" t="n">
         <v>0.08333</v>
@@ -3469,22 +3489,22 @@
         <v>0.5121</v>
       </c>
       <c r="V26" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="W26" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
       <c r="X26" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>6405-14-12-O</t>
+          <t>6405-12-12-O</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 3/16-12 (male ORB) x 3/4-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3494,7 +3514,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>1 3/16-12 (male ORB)</t>
+          <t>1 1/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3504,54 +3524,54 @@
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1788 Overall Length = 1.780 (table had 1.6) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ORB -14 groove width MEASURED 0.125 on the Brennan 6400-14-14-O STEP (2026-09-25, single source)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.59~1.590; HEXB@HEX=1.38~1.375; D3@BORE=0.61~0.609</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>6405-14-12-O</t>
+          <t>6405-12-12-O</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6405-16-04-O</t>
+          <t>6405-12-16-O</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="C27" t="n">
-        <v>0.86603</v>
+        <v>0.94108</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="E27" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F27" t="n">
         <v>0.469</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="H27" t="n">
         <v>0.125</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="J27" t="n">
         <v>0.08333</v>
@@ -3569,43 +3589,43 @@
         <v>0.08333</v>
       </c>
       <c r="O27" t="n">
-        <v>0.43</v>
+        <v>1.14</v>
       </c>
       <c r="P27" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.43</v>
+        <v>1.14</v>
       </c>
       <c r="R27" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0556</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>0.215</v>
+        <v>0.57</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2594</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>1.14</v>
+        <v>2.03</v>
       </c>
       <c r="W27" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="X27" t="n">
-        <v>0.47</v>
+        <v>0.89</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>6405-16-04-O</t>
+          <t>6405-12-16-O</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 1/4-18 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 1/16-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3615,12 +3635,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>1 5/16-12 (male ORB)</t>
+          <t>1 1/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -3630,49 +3650,44 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1789 Overall Length = 1.140 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.470 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.14 looks suspect for this size (built as printed)</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1787 Overall Length = 2.030 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>6405-16-04-O</t>
+          <t>6405-12-16-O</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6405-16-12-O</t>
+          <t>6405-14-12-O</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="C28" t="n">
-        <v>0.86603</v>
+        <v>0.79674</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="E28" t="n">
-        <v>0.65625</v>
+        <v>0.59375</v>
       </c>
       <c r="F28" t="n">
         <v>0.469</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5975</v>
+        <v>0.535</v>
       </c>
       <c r="H28" t="n">
         <v>0.125</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3125</v>
+        <v>1.1875</v>
       </c>
       <c r="J28" t="n">
         <v>0.08333</v>
@@ -3711,22 +3726,22 @@
         <v>0.5121</v>
       </c>
       <c r="V28" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="W28" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="X28" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>6405-16-12-O</t>
+          <t>6405-14-12-O</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 3/4-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 3/16-12 (male ORB) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3736,7 +3751,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>1 5/16-12 (male ORB)</t>
+          <t>1 3/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3751,29 +3766,34 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1788 Overall Length = 1.780 (table had 1.6) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ORB -14 groove width MEASURED 0.125 on the Brennan 6400-14-14-O STEP (2026-09-25, single source)</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>6405-16-12-O</t>
+          <t>6405-14-12-O</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6405-16-16-O</t>
+          <t>6405-16-04-O</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="C29" t="n">
-        <v>0.94108</v>
+        <v>0.86603</v>
       </c>
       <c r="D29" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="n">
         <v>0.65625</v>
@@ -3806,43 +3826,43 @@
         <v>0.08333</v>
       </c>
       <c r="O29" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.14</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.6395999999999999</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.9</v>
-      </c>
       <c r="W29" t="n">
-        <v>0.84</v>
+        <v>0.43</v>
       </c>
       <c r="X29" t="n">
-        <v>0.76</v>
+        <v>0.47</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>6405-16-16-O</t>
+          <t>6405-16-04-O</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3857,7 +3877,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1/4-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -3867,29 +3887,34 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1789 Overall Length = 1.140 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.470 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.14 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>6405-16-16-O</t>
+          <t>6405-16-04-O</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6405-16-20-O</t>
+          <t>6405-16-06-O</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.27</v>
+        <v>1.13</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1547</v>
+        <v>0.86603</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="E30" t="n">
         <v>0.65625</v>
@@ -3922,43 +3947,43 @@
         <v>0.08333</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>0.57</v>
       </c>
       <c r="P30" t="n">
-        <v>1.16</v>
+        <v>0.68</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.48</v>
+        <v>0.57</v>
       </c>
       <c r="R30" t="n">
-        <v>1.16</v>
+        <v>0.68</v>
       </c>
       <c r="S30" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0556</v>
       </c>
       <c r="T30" t="n">
-        <v>0.74</v>
+        <v>0.285</v>
       </c>
       <c r="U30" t="n">
-        <v>0.8096</v>
+        <v>0.3294</v>
       </c>
       <c r="V30" t="n">
-        <v>2.27</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
-        <v>0.84</v>
+        <v>0.57</v>
       </c>
       <c r="X30" t="n">
-        <v>1.11</v>
+        <v>0.45</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>6405-16-20-O</t>
+          <t>6405-16-06-O</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3998,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -3983,44 +4008,49 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1794 Overall Length = 2.270 (table had 2.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1790 = 0.844 (table had 0.57) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.57 = the -06 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L31@DRIVE 1 -&gt; 1.13 | AS-PRINTED WARNING: port drill depth P1 0.68 leaves only 0.450 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.13 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>6405-16-20-O</t>
+          <t>6405-16-06-O</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6405-20-08-O</t>
+          <t>6405-16-08-O</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="C31" t="n">
-        <v>1.08542</v>
+        <v>0.86603</v>
       </c>
       <c r="D31" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F31" t="n">
         <v>0.469</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H31" t="n">
         <v>0.125</v>
       </c>
       <c r="I31" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J31" t="n">
         <v>0.08333</v>
@@ -4059,22 +4089,22 @@
         <v>0.4071</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="W31" t="n">
-        <v>0.649</v>
+        <v>0.7</v>
       </c>
       <c r="X31" t="n">
-        <v>0.3</v>
+        <v>0.82</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>6405-20-08-O</t>
+          <t>6405-16-08-O</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1/2-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4084,7 +4114,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4099,49 +4129,49 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1796 Side 1 ID = 0.649 (table had 0.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>D=0.7 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.300 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
+          <t>D=0.7 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1791 = 1.720 (table had 1.47); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1791 = 0.844 (table had 0.7) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.7 = the -08 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>6405-20-08-O</t>
+          <t>6405-16-08-O</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6405-20-12-O</t>
+          <t>6405-16-12-O</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="C32" t="n">
-        <v>1.08542</v>
+        <v>0.86603</v>
       </c>
       <c r="D32" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F32" t="n">
         <v>0.469</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H32" t="n">
         <v>0.125</v>
       </c>
       <c r="I32" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J32" t="n">
         <v>0.08333</v>
@@ -4180,22 +4210,22 @@
         <v>0.5121</v>
       </c>
       <c r="V32" t="n">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>0.854</v>
+        <v>0.84</v>
       </c>
       <c r="X32" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>6405-20-12-O</t>
+          <t>6405-16-12-O</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 3/4-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4205,7 +4235,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4215,54 +4245,54 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1797 Side 1 ID = 0.854 (table had 0.91) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.290 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.62~1.620; HEXB@HEX=1.5~1.500; D3@BORE=0.84~0.840</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>6405-20-12-O</t>
+          <t>6405-16-12-O</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6405-20-16-O</t>
+          <t>6405-16-16-O</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="C33" t="n">
-        <v>1.08542</v>
+        <v>0.94108</v>
       </c>
       <c r="D33" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F33" t="n">
         <v>0.469</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H33" t="n">
         <v>0.125</v>
       </c>
       <c r="I33" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J33" t="n">
         <v>0.08333</v>
@@ -4301,22 +4331,22 @@
         <v>0.6395999999999999</v>
       </c>
       <c r="V33" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="X33" t="n">
-        <v>0.06</v>
+        <v>0.76</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>6405-20-16-O</t>
+          <t>6405-16-16-O</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4326,7 +4356,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4336,7 +4366,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -4346,23 +4376,23 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>OMi Overall Length 1.000 NOT applied (2026-09-25): exactly 1.000 like the 6410 placeholders (audit Q8); as 1.000 the pocket P1 1.14 would not fit - user decision pending | AS-PRINTED WARNING: port drill depth P1 1.14 leaves only 0.060 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L31@DRIVE=1.9~1.900; HEXB@HEX=1.63~1.625; D3@BORE=0.84~0.844</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>6405-20-16-O</t>
+          <t>6405-16-16-O</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6405-20-20-O</t>
+          <t>6405-16-20-O</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="C34" t="n">
         <v>1.1547</v>
@@ -4371,19 +4401,19 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F34" t="n">
         <v>0.469</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5975</v>
       </c>
       <c r="H34" t="n">
         <v>0.125</v>
       </c>
       <c r="I34" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="J34" t="n">
         <v>0.08333</v>
@@ -4422,22 +4452,22 @@
         <v>0.8096</v>
       </c>
       <c r="V34" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="X34" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>6405-20-20-O</t>
+          <t>6405-16-20-O</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/16-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4447,7 +4477,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>1 5/8-12 (male ORB)</t>
+          <t>1 5/16-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4462,29 +4492,29 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1799 Overall Length = 1.970 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1794 Overall Length = 2.270 (table had 2.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>6405-20-20-O</t>
+          <t>6405-16-20-O</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6405-20-24-O</t>
+          <t>6405-20-08-O</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="C35" t="n">
-        <v>1.37409</v>
+        <v>1.08542</v>
       </c>
       <c r="D35" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="E35" t="n">
         <v>0.8125</v>
@@ -4517,43 +4547,43 @@
         <v>0.08333</v>
       </c>
       <c r="O35" t="n">
-        <v>1.72</v>
+        <v>0.7</v>
       </c>
       <c r="P35" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.72</v>
+        <v>0.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="S35" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>0.86</v>
+        <v>0.35</v>
       </c>
       <c r="U35" t="n">
-        <v>0.9296</v>
+        <v>0.4071</v>
       </c>
       <c r="V35" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>1.08</v>
+        <v>0.649</v>
       </c>
       <c r="X35" t="n">
-        <v>1.14</v>
+        <v>0.3</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>6405-20-24-O</t>
+          <t>6405-20-08-O</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4568,7 +4598,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -4578,44 +4608,49 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1800 Overall Length = 2.300 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1796 Side 1 ID = 0.649 (table had 0.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>D=0.7 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.300 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>6405-20-24-O</t>
+          <t>6405-20-08-O</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6405-24-12-O</t>
+          <t>6405-20-12-O</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="C36" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D36" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F36" t="n">
         <v>0.469</v>
       </c>
       <c r="G36" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H36" t="n">
         <v>0.125</v>
       </c>
       <c r="I36" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J36" t="n">
         <v>0.08333</v>
@@ -4654,22 +4689,22 @@
         <v>0.5121</v>
       </c>
       <c r="V36" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>0.91</v>
+        <v>0.854</v>
       </c>
       <c r="X36" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>6405-24-12-O</t>
+          <t>6405-20-12-O</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 3/4-14 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4679,7 +4714,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4694,49 +4729,49 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1801 Overall Length = 1.270 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1797 Side 1 ID = 0.854 (table had 0.91) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.360 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.27 looks suspect for this size (built as printed)</t>
+          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.290 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>6405-24-12-O</t>
+          <t>6405-20-12-O</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6405-24-16-O</t>
+          <t>6405-20-16-O</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="C37" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D37" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F37" t="n">
         <v>0.469</v>
       </c>
       <c r="G37" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H37" t="n">
         <v>0.125</v>
       </c>
       <c r="I37" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J37" t="n">
         <v>0.08333</v>
@@ -4775,22 +4810,22 @@
         <v>0.6395999999999999</v>
       </c>
       <c r="V37" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="W37" t="n">
         <v>1.08</v>
       </c>
       <c r="X37" t="n">
-        <v>0.61</v>
+        <v>0.06</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>6405-24-16-O</t>
+          <t>6405-20-16-O</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4800,7 +4835,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4815,49 +4850,49 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1802 Overall Length = 1.750 (table had 1); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1802 Side 1 ID = 1.080 (table had 1.14) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>D=1.14 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 1.14 leaves only 0.610 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.75 looks suspect for this size (built as printed)</t>
+          <t>OMi Overall Length 1.000 NOT applied (2026-09-25): exactly 1.000 like the 6410 placeholders (audit Q8); as 1.000 the pocket P1 1.14 would not fit - user decision pending | OMi answer 2026-10-18 (staged, not shipped): OMi's real Overall Length 1.2 (Lengths to check!E3; website file said 1.000, a filler) = the Air-Way L31 1.2 already in this row -&gt; no change; OMi and Air-Way agree on the length | AS-PRINTED WARNING: port drill depth P1 1.14 leaves only 0.060 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>6405-24-16-O</t>
+          <t>6405-20-16-O</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6405-24-20-O</t>
+          <t>6405-20-20-O</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="C38" t="n">
-        <v>1.22976</v>
+        <v>1.1547</v>
       </c>
       <c r="D38" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F38" t="n">
         <v>0.469</v>
       </c>
       <c r="G38" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H38" t="n">
         <v>0.125</v>
       </c>
       <c r="I38" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J38" t="n">
         <v>0.08333</v>
@@ -4896,22 +4931,22 @@
         <v>0.8096</v>
       </c>
       <c r="V38" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="W38" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>6405-24-20-O</t>
+          <t>6405-20-20-O</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4921,7 +4956,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4936,23 +4971,23 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1803 Overall Length = 2.160 (table had 1.85) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1799 Overall Length = 1.970 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>6405-24-20-O</t>
+          <t>6405-20-20-O</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6405-24-24-O</t>
+          <t>6405-20-24-O</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="C39" t="n">
         <v>1.37409</v>
@@ -4961,19 +4996,19 @@
         <v>2.38</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F39" t="n">
         <v>0.469</v>
       </c>
       <c r="G39" t="n">
-        <v>0.878</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="H39" t="n">
         <v>0.125</v>
       </c>
       <c r="I39" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="J39" t="n">
         <v>0.08333</v>
@@ -5012,22 +5047,22 @@
         <v>0.9296</v>
       </c>
       <c r="V39" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="W39" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>6405-24-24-O</t>
+          <t>6405-20-24-O</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 1 1/2-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 5/8-12 (male ORB) x 1 1/2-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5037,7 +5072,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>1 7/8-12 (male ORB)</t>
+          <t>1 5/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5052,44 +5087,44 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1804 Overall Length = 2.160 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1800 Overall Length = 2.300 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>6405-24-24-O</t>
+          <t>6405-20-24-O</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6405-32-20-O</t>
+          <t>6405-24-12-O</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="C40" t="n">
-        <v>1.58771</v>
+        <v>1.22976</v>
       </c>
       <c r="D40" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="E40" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="F40" t="n">
         <v>0.469</v>
       </c>
       <c r="G40" t="n">
-        <v>1.1905</v>
+        <v>0.878</v>
       </c>
       <c r="H40" t="n">
         <v>0.125</v>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="J40" t="n">
         <v>0.08333</v>
@@ -5107,43 +5142,43 @@
         <v>0.08333</v>
       </c>
       <c r="O40" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="P40" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="R40" t="n">
-        <v>1.16</v>
+        <v>0.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>0.74</v>
+        <v>0.455</v>
       </c>
       <c r="U40" t="n">
-        <v>0.8096</v>
+        <v>0.5121</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="W40" t="n">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="X40" t="n">
-        <v>0.84</v>
+        <v>0.36</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>6405-32-20-O</t>
+          <t>6405-24-12-O</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 2 1/2-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5153,12 +5188,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2 1/2-12 (male ORB)</t>
+          <t>1 7/8-12 (male ORB)</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>3/4-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -5168,49 +5203,49 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1801 Overall Length = 1.270 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.360 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.27 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>6405-32-20-O</t>
+          <t>6405-24-12-O</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6405-32-32-O</t>
+          <t>6405-24-16-O</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="C41" t="n">
-        <v>1.66277</v>
+        <v>1.22976</v>
       </c>
       <c r="D41" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="E41" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="F41" t="n">
         <v>0.469</v>
       </c>
       <c r="G41" t="n">
-        <v>1.1905</v>
+        <v>0.878</v>
       </c>
       <c r="H41" t="n">
         <v>0.125</v>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="J41" t="n">
         <v>0.08333</v>
@@ -5228,76 +5263,550 @@
         <v>0.08333</v>
       </c>
       <c r="O41" t="n">
-        <v>2.19</v>
+        <v>1.14</v>
       </c>
       <c r="P41" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.19</v>
+        <v>1.14</v>
       </c>
       <c r="R41" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S41" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="T41" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>6405-24-16-O</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1802 Overall Length = 1.750 (table had 1); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1802 Side 1 ID = 1.080 (table had 1.14) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>D=1.14 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 1.14 leaves only 0.610 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.75 looks suspect for this size (built as printed)</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>6405-24-16-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6405-24-20-O</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="V42" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>6405-24-20-O</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1803 Overall Length = 2.160 (table had 1.85) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>6405-24-20-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6405-24-24-O</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.37409</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>6405-24-24-O</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 1 7/8-12 (male ORB) x 1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1804 Overall Length = 2.160 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>6405-24-24-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6405-32-20-O</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="V44" t="n">
+        <v>2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>6405-32-20-O</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 2 1/2-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>6405-32-20-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6405-32-32-O</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T45" t="n">
         <v>1.095</v>
       </c>
-      <c r="U41" t="n">
+      <c r="U45" t="n">
         <v>1.1646</v>
       </c>
-      <c r="V41" t="n">
+      <c r="V45" t="n">
         <v>2.24</v>
       </c>
-      <c r="W41" t="n">
+      <c r="W45" t="n">
         <v>1.78</v>
       </c>
-      <c r="X41" t="n">
+      <c r="X45" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>6405-32-32-O</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>Straight Thread (ORB) x Female Pipe Adapter, 2 1/2-12 (male ORB) x 2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>6405</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>2 1/2-12 (male ORB)</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AE45" t="inlineStr">
         <is>
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1808 Overall Length = 2.240 (table had 2.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)</t>
         </is>
       </c>
-      <c r="AG41" t="inlineStr">
+      <c r="AG45" t="inlineStr">
         <is>
           <t>6405-32-32-O</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_6405_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6405_SW2.xlsx
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="C2" t="n">
         <v>0.65241</v>
@@ -645,13 +645,13 @@
         <v>0.4071</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
         <v>0.39</v>
       </c>
       <c r="X2" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -685,7 +685,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1776 Overall Length = 1.470 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1776 Overall Length = 1.470 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.63 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.47) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.47 -&gt; Air-Way 1.63</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1291,7 +1296,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="C8" t="n">
         <v>0.50807</v>
@@ -1351,13 +1356,13 @@
         <v>0.3294</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
         <v>0.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1391,7 +1396,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1766 Overall Length = 1.350 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1766 Overall Length = 1.350 (table had 1.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.25 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.35 -&gt; Air-Way 1.25</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1407,7 +1417,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C9" t="n">
         <v>0.36373</v>
@@ -1467,13 +1477,13 @@
         <v>0.1946</v>
       </c>
       <c r="V9" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1507,7 +1517,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1767 Overall Length = 0.990 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1767 Overall Length = 0.990 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 0.94 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 0.99 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1523,7 +1538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="C10" t="n">
         <v>0.43301</v>
@@ -1583,13 +1598,13 @@
         <v>0.2594</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W10" t="n">
         <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1623,7 +1638,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1768 Overall Length = 1.200 (table had 1.15) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1768 Overall Length = 1.200 (table had 1.15) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.15 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.2 -&gt; Air-Way 1.15</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1639,7 +1659,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="C11" t="n">
         <v>0.39837</v>
@@ -1699,13 +1719,13 @@
         <v>0.1946</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>0.73</v>
       </c>
       <c r="W11" t="n">
-        <v>0.297</v>
+        <v>0.33</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1739,12 +1759,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1769 Overall Length = 1.020 (table had 0.73); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1769 Side 1 ID = 0.297 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1769 Overall Length = 1.020 (table had 0.73); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1769 Side 1 ID = 0.297 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 0.73 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.02) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D3@BORE: Air-Way 0.33 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.297) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.297 - column bleed suspected, as-printed</t>
+          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.297 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.02 -&gt; Air-Way 0.73 | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.297 -&gt; Air-Way 0.33 | AS-PRINTED WARNING: port drill depth P1 0.46 leaves only 0.270 to the far tip, inside the other end's thread/groove region (0.395) - Air-Way L 0.73 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1760,13 +1780,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="C12" t="n">
-        <v>0.43301</v>
+        <v>0.39837</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>0.28125</v>
@@ -1820,13 +1840,13 @@
         <v>0.2594</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
         <v>0.3</v>
       </c>
       <c r="X12" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1860,12 +1880,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1770 Overall Length = 1.090 (table had 1.18); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1770 Hex Flat = 0.750 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1770 Overall Length = 1.090 (table had 1.18); HEXB@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1770 Hex Flat = 0.750 (table had 0.69) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.18 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.09) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; HEXB@HEX: Air-Way 0.69 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.75) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.420 to the far tip, inside the other end's thread/groove region (0.395) - Air-Way L 1.09 looks suspect for this size (built as printed)</t>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.09 -&gt; Air-Way 1.18 | 2026-10-20 Air-Way first: HEXB@HEX OMi/Brennan 0.75 -&gt; Air-Way 0.69</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1881,7 +1901,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="C13" t="n">
         <v>0.50807</v>
@@ -1941,13 +1961,13 @@
         <v>0.3294</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
         <v>0.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1981,7 +2001,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1771 Overall Length = 1.330 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1771 Overall Length = 1.330 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.31 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.33) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.33 -&gt; Air-Way 1.31</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2181,7 +2206,7 @@
         <v>0.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="X15" t="n">
         <v>0.34</v>
@@ -2218,12 +2243,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1773 Side 1 ID = 0.315 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1773 Side 1 ID = 0.315 (table had 0.33) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.33 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.315) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.46 leaves only 0.340 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 0.8 looks suspect for this size (built as printed)</t>
+          <t>D=0.33 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.315 -&gt; Air-Way 0.33 | AS-PRINTED WARNING: port drill depth P1 0.46 leaves only 0.340 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 0.8 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -2302,7 +2327,7 @@
         <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0.391</v>
+        <v>0.43</v>
       </c>
       <c r="X16" t="n">
         <v>0.35</v>
@@ -2339,12 +2364,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1774 Side 1 ID = 0.391 (table had 0.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1774 Side 1 ID = 0.391 (table had 0.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.43 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.350 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 1.02 looks suspect for this size (built as printed)</t>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.391 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.43 | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.350 to the far tip, inside the other end's thread/groove region (0.438) - Air-Way L 1.02 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2360,7 +2385,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="C17" t="n">
         <v>0.50807</v>
@@ -2420,13 +2445,13 @@
         <v>0.3294</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
         <v>0.39</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2460,7 +2485,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1775 Overall Length = 1.280 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1775 Overall Length = 1.280 (table had 1.26) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.26 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.28 -&gt; Air-Way 1.26</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2476,7 +2506,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="C18" t="n">
         <v>0.79674</v>
@@ -2536,13 +2566,13 @@
         <v>0.5121</v>
       </c>
       <c r="V18" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
         <v>0.39</v>
       </c>
       <c r="X18" t="n">
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2576,7 +2606,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1777 Overall Length = 1.780 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1777 Overall Length = 1.780 (table had 1.63) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.63 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.63</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2713,7 +2748,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="C20" t="n">
         <v>0.57735</v>
@@ -2773,13 +2808,13 @@
         <v>0.3294</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
         <v>0.48</v>
       </c>
       <c r="X20" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2813,7 +2848,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1780 Overall Length = 1.400 (table had 1.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1780 Overall Length = 1.400 (table had 1.28) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.28 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.4 -&gt; Air-Way 1.28</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2950,7 +2990,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="C22" t="n">
         <v>0.79674</v>
@@ -3010,13 +3050,13 @@
         <v>0.5121</v>
       </c>
       <c r="V22" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="W22" t="n">
         <v>0.48</v>
       </c>
       <c r="X22" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -3050,7 +3090,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1782 Overall Length = 1.710 (table had 1.64) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1782 Overall Length = 1.710 (table had 1.64) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.64 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.71) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.71 -&gt; Air-Way 1.64</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -3187,7 +3232,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="C24" t="n">
         <v>0.7216900000000001</v>
@@ -3247,13 +3292,13 @@
         <v>0.3294</v>
       </c>
       <c r="V24" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="W24" t="n">
         <v>0.57</v>
       </c>
       <c r="X24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -3287,12 +3332,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1784 Overall Length = 1.490 (table had 1.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1784 Overall Length = 1.490 (table had 1.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.09 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.49) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.57); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.609 - column bleed suspected, as-printed | OMi Side 1 ID 0.609 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 0.57); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.49 -&gt; Air-Way 1.09 | AS-PRINTED WARNING: port drill depth P1 0.68 leaves only 0.410 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.09 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3308,7 +3353,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="C25" t="n">
         <v>0.7216900000000001</v>
@@ -3368,13 +3413,13 @@
         <v>0.4071</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
         <v>0.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -3408,12 +3453,12 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1785 Overall Length = 1.410 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1785 Overall Length = 1.410 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.5 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.510 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.41 looks suspect for this size (built as printed)</t>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.5 | AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.600 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.5 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3550,7 +3595,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="C27" t="n">
         <v>0.94108</v>
@@ -3610,13 +3655,13 @@
         <v>0.6395999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="W27" t="n">
         <v>0.61</v>
       </c>
       <c r="X27" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -3650,7 +3695,12 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1787 Overall Length = 2.030 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1787 Overall Length = 2.030 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.95 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.03) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.03 -&gt; Air-Way 1.95</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3666,7 +3716,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="C28" t="n">
         <v>0.79674</v>
@@ -3726,13 +3776,13 @@
         <v>0.5121</v>
       </c>
       <c r="V28" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="W28" t="n">
         <v>0.72</v>
       </c>
       <c r="X28" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3766,12 +3816,12 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1788 Overall Length = 1.780 (table had 1.6) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1788 Overall Length = 1.780 (table had 1.6) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.6 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ORB -14 groove width MEASURED 0.125 on the Brennan 6400-14-14-O STEP (2026-09-25, single source)</t>
+          <t>ORB -14 groove width MEASURED 0.125 on the Brennan 6400-14-14-O STEP (2026-09-25, single source)| 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.78 -&gt; Air-Way 1.6</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3787,7 +3837,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="C29" t="n">
         <v>0.86603</v>
@@ -3847,13 +3897,13 @@
         <v>0.2594</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W29" t="n">
         <v>0.43</v>
       </c>
       <c r="X29" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3887,12 +3937,12 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1789 Overall Length = 1.140 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1789 Overall Length = 1.140 (table had 1.12) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.12 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.470 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.14 looks suspect for this size (built as printed)</t>
+          <t>D=0.43 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.12 | AS-PRINTED WARNING: port drill depth P1 0.67 leaves only 0.450 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.12 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -3908,7 +3958,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>0.86603</v>
@@ -3968,13 +4018,13 @@
         <v>0.3294</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
         <v>0.57</v>
       </c>
       <c r="X30" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -4008,12 +4058,12 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: Air-Way 1 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.13) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1790 = 0.844 (table had 0.57) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.57 = the -06 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L31@DRIVE 1 -&gt; 1.13 | AS-PRINTED WARNING: port drill depth P1 0.68 leaves only 0.450 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.13 looks suspect for this size (built as printed)</t>
+          <t>D=0.57 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1790 = 0.844 (table had 0.57) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.57 = the -06 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L31@DRIVE 1 -&gt; 1.13 | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.13 -&gt; Air-Way 1 | AS-PRINTED WARNING: port drill depth P1 0.68 leaves only 0.320 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -4029,7 +4079,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="C31" t="n">
         <v>0.86603</v>
@@ -4089,13 +4139,13 @@
         <v>0.4071</v>
       </c>
       <c r="V31" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
         <v>0.7</v>
       </c>
       <c r="X31" t="n">
-        <v>0.82</v>
+        <v>0.57</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -4129,12 +4179,12 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: Air-Way 1.47 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>D=0.7 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1791 = 1.720 (table had 1.47); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1791 = 0.844 (table had 0.7) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.7 = the -08 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied</t>
+          <t>D=0.7 equals tap drill and differs from dash-expected bore 0.844 - column bleed suspected, as-printed | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1791 = 1.720 (table had 1.47); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1791 = 0.844 (table had 0.7) | Brennan TFA TFA-p016-t01: agrees on L31@DRIVE, HEXB@HEX | 2026-10-18 rebase (A11 Q-BOREWIDE yes: cap at the port drill, report to OMi): D3@BORE stays 0.7 = the -08 female pipe tap drill; OMi 0.844 (= Brennan B DRILL) is wider than the port it runs into - the OMi D3@BORE value above is NOT applied | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.47 | AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.570 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.47 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -4392,7 +4442,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="C34" t="n">
         <v>1.1547</v>
@@ -4452,13 +4502,13 @@
         <v>0.8096</v>
       </c>
       <c r="V34" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="W34" t="n">
         <v>0.84</v>
       </c>
       <c r="X34" t="n">
-        <v>1.11</v>
+        <v>0.93</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -4492,7 +4542,12 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1794 Overall Length = 2.270 (table had 2.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1794 Overall Length = 2.270 (table had 2.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2.09 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.27 -&gt; Air-Way 2.09</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -4571,7 +4626,7 @@
         <v>1.2</v>
       </c>
       <c r="W35" t="n">
-        <v>0.649</v>
+        <v>0.7</v>
       </c>
       <c r="X35" t="n">
         <v>0.3</v>
@@ -4608,12 +4663,12 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1796 Side 1 ID = 0.649 (table had 0.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1796 Side 1 ID = 0.649 (table had 0.7) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.7 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.649) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>D=0.7 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.300 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
+          <t>D=0.7 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.649 -&gt; Air-Way 0.7 | AS-PRINTED WARNING: port drill depth P1 0.9 leaves only 0.300 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -4692,7 +4747,7 @@
         <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>0.854</v>
+        <v>0.91</v>
       </c>
       <c r="X36" t="n">
         <v>0.29</v>
@@ -4729,12 +4784,12 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1797 Side 1 ID = 0.854 (table had 0.91) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1797 Side 1 ID = 0.854 (table had 0.91) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 0.91 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.854) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.290 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
+          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.078 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 0.854 -&gt; Air-Way 0.91 | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.290 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.2 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -4871,7 +4926,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="C38" t="n">
         <v>1.1547</v>
@@ -4931,13 +4986,13 @@
         <v>0.8096</v>
       </c>
       <c r="V38" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="W38" t="n">
         <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -4971,7 +5026,12 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1799 Overall Length = 1.970 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1799 Overall Length = 1.970 (table had 1.95) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.95 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.97) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.97 -&gt; Air-Way 1.95</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
@@ -4987,7 +5047,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="C39" t="n">
         <v>1.37409</v>
@@ -5047,13 +5107,13 @@
         <v>0.9296</v>
       </c>
       <c r="V39" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="W39" t="n">
         <v>1.08</v>
       </c>
       <c r="X39" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -5087,7 +5147,12 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1800 Overall Length = 2.300 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1800 Overall Length = 2.300 (table had 2.27) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2.27 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.3 -&gt; Air-Way 2.27</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -5103,7 +5168,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>1.22976</v>
@@ -5163,13 +5228,13 @@
         <v>0.5121</v>
       </c>
       <c r="V40" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
         <v>0.91</v>
       </c>
       <c r="X40" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -5203,12 +5268,12 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1801 Overall Length = 1.270 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1801 Overall Length = 1.270 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.360 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.27 looks suspect for this size (built as printed)</t>
+          <t>D=0.91 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 1.27 -&gt; Air-Way 1 | AS-PRINTED WARNING: port drill depth P1 0.91 leaves only 0.090 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
@@ -5287,7 +5352,7 @@
         <v>1.75</v>
       </c>
       <c r="W41" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X41" t="n">
         <v>0.61</v>
@@ -5324,12 +5389,12 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1802 Overall Length = 1.750 (table had 1); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1802 Side 1 ID = 1.080 (table had 1.14) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>[BRENNAN-CELL 2026-10-20: L31@DRIVE] ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1802 Overall Length = 1.750 (table had 1); D3@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1802 Side 1 ID = 1.080 (table had 1.14) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D3@BORE: Air-Way 1.14 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L31@DRIVE: Brennan TFA catalog p16 table TFA-p016-t01 "MORB-FP STRAIGHT" row 6405-24-16-O col "L LGTH" = 1.75 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>D=1.14 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | AS-PRINTED WARNING: port drill depth P1 1.14 leaves only 0.610 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.75 looks suspect for this size (built as printed)</t>
+          <t>D=1.14 equals tap drill and differs from dash-expected bore 1.312 - column bleed suspected, as-printed | 2026-10-20 Air-Way first: D3@BORE OMi/Brennan 1.08 -&gt; Air-Way 1.14 | 2026-10-20 L31@DRIVE = Brennan 1.75 (Air-Way 1.0 cannot be built: Air-Way L 1.00 &lt; the 1-NPTF pocket depth 1.14: no room for a bore (generator BLOCKED)) | AS-PRINTED WARNING: port drill depth P1 1.14 leaves only 0.610 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.75 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
@@ -5345,7 +5410,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="C42" t="n">
         <v>1.22976</v>
@@ -5405,13 +5470,13 @@
         <v>0.8096</v>
       </c>
       <c r="V42" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="W42" t="n">
         <v>1.31</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -5445,7 +5510,12 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1803 Overall Length = 2.160 (table had 1.85) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1803 Overall Length = 2.160 (table had 1.85) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.85 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.16 -&gt; Air-Way 1.85</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
@@ -5461,7 +5531,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
         <v>1.37409</v>
@@ -5521,13 +5591,13 @@
         <v>0.9296</v>
       </c>
       <c r="V43" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="W43" t="n">
         <v>1.31</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -5561,7 +5631,12 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1804 Overall Length = 2.160 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1804 Overall Length = 2.160 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.16) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.16 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
@@ -5577,7 +5652,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="C44" t="n">
         <v>1.58771</v>
@@ -5637,13 +5712,13 @@
         <v>0.8096</v>
       </c>
       <c r="V44" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="W44" t="n">
         <v>1.48</v>
       </c>
       <c r="X44" t="n">
-        <v>0.84</v>
+        <v>0.27</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -5677,12 +5752,12 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.43 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending</t>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2 -&gt; Air-Way 1.43 | AS-PRINTED WARNING: port drill depth P1 1.16 leaves only 0.270 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.43 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
@@ -5698,7 +5773,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="C45" t="n">
         <v>1.66277</v>
@@ -5758,13 +5833,13 @@
         <v>1.1646</v>
       </c>
       <c r="V45" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="W45" t="n">
         <v>1.78</v>
       </c>
       <c r="X45" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -5798,12 +5873,12 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1808 Overall Length = 2.240 (table had 2.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1808 Overall Length = 2.240 (table had 2.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2.23 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.24) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)</t>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)| 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.24 -&gt; Air-Way 2.23</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6405_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6405_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AG46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5648,7 +5648,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6405-32-20-O</t>
+          <t>6405-32-16-O</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -5691,43 +5691,43 @@
         <v>0.08333</v>
       </c>
       <c r="O44" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="P44" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="R44" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S44" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="U44" t="n">
-        <v>0.8096</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V44" t="n">
         <v>1.43</v>
       </c>
       <c r="W44" t="n">
-        <v>1.48</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>6405-32-20-O</t>
+          <t>6405-32-16-O</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>Straight Thread (ORB) x Female Pipe Adapter, 2 1/2-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 2 1/2-12 (male ORB) x 1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF (female)</t>
+          <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -5752,34 +5752,34 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.43 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L31 / hex / D3 = OMi WebsitePartsInfo2026.xlsx Items row 1805; tap drill 1.14 = Air-Way -16 (A1); -32 ORB end from the end library (ORB[32]: 6408-32-O-SOLID row + groove width 0.125 measured on the Brennan 6400-32-32-O STEP, A18 - ORB_GRVW left empty on purpose, the generator applies the library value); FPT_P1 from the 2405 end library | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2 -&gt; Air-Way 1.43 | AS-PRINTED WARNING: port drill depth P1 1.16 leaves only 0.270 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.43 looks suspect for this size (built as printed)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1805 + A1 tap drill; D3 OMi 1.080 vs Brennan TFA p16 B DRILL 1.156 - OMi kept (source order), tell the user | AS-PRINTED WARNING: port drill depth P1 1.14 leaves only 0.290 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.43 looks suspect for this size (built as printed)</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>6405-32-20-O</t>
+          <t>6405-32-16-O</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6405-32-32-O</t>
+          <t>6405-32-20-O</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.23</v>
+        <v>1.43</v>
       </c>
       <c r="C45" t="n">
-        <v>1.66277</v>
+        <v>1.58771</v>
       </c>
       <c r="D45" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="E45" t="n">
         <v>1.25</v>
@@ -5812,76 +5812,197 @@
         <v>0.08333</v>
       </c>
       <c r="O45" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="P45" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="R45" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S45" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="T45" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>6405-32-20-O</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Straight Thread (ORB) x Female Pipe Adapter, 2 1/2-12 (male ORB) x 1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (male ORB)</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1806 Overall Length = 2.000 (table had 1.43) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 1.43 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source); D=1.48 equals tap drill and differs from dash-expected bore 1.781 - column bleed suspected, as-printed | OMi Side 1 ID 1.781 NOT applied (2026-09-25): wider than the female port it runs into (pocket (tap drill) 1.48); in the Brennan 6410-12-08-O / -24-20-O STEPs the through-bore stays below the port minor - geometry conflict, user decision pending | 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2 -&gt; Air-Way 1.43 | AS-PRINTED WARNING: port drill depth P1 1.16 leaves only 0.270 to the far tip, inside the other end's thread/groove region (0.594) - Air-Way L 1.43 looks suspect for this size (built as printed)</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>6405-32-20-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6405-32-32-O</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="T46" t="n">
         <v>1.095</v>
       </c>
-      <c r="U45" t="n">
+      <c r="U46" t="n">
         <v>1.1646</v>
       </c>
-      <c r="V45" t="n">
+      <c r="V46" t="n">
         <v>2.23</v>
       </c>
-      <c r="W45" t="n">
+      <c r="W46" t="n">
         <v>1.78</v>
       </c>
-      <c r="X45" t="n">
+      <c r="X46" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>6405-32-32-O</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>Straight Thread (ORB) x Female Pipe Adapter, 2 1/2-12 (male ORB) x 2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>6405</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>2 1/2-12 (male ORB)</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AE45" t="inlineStr">
+      <c r="AE46" t="inlineStr">
         <is>
           <t>ORB end: sourced; female NPTF: tap drill (AW) + P1 (MS51503 transfer, ASSUMED); L31/hex: Air-Way single source; L31@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1808 Overall Length = 2.240 (table had 2.23) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L31@DRIVE: Air-Way 2.23 (log (no Air-Way raw extract in the repo); OMi file / Brennan 2.24) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end as 6401; female drill depth = FPT_P1 from the review table (MS51503 P1 max), thread cut to full drill depth (ASSUMPTION); Brennan 5405-08-08 STEP (2026-09-23) confirms 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED for -08 only; thread taper depth in that STEP is 0.750, tap drill dia 0.718, drill point 120 deg); bore D3 from the ORB tip to the pocket bottom</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr">
+      <c r="AF46" t="inlineStr">
         <is>
           <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)| 2026-10-20 Air-Way first: L31@DRIVE OMi/Brennan 2.24 -&gt; Air-Way 2.23</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>6405-32-32-O</t>
         </is>
